--- a/05-Power-Budget/PowerBudget.xlsx
+++ b/05-Power-Budget/PowerBudget.xlsx
@@ -1,33 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e6f92803327c9ad0/Documents/EGR 304/jsilber27_EGR304_F26.github.io-1/docs/05-Power-Budget/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_0454703C4A55ECA9EDEB81173C2076994B823C75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{876A6AB5-8ECC-43B4-BAE3-D2371E6192F0}"/>
+  <bookViews>
+    <workbookView xWindow="5124" yWindow="1956" windowWidth="16356" windowHeight="13296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
   <si>
     <t>Power Budget</t>
   </si>
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">Team Number: </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
       </rPr>
       <t>205</t>
     </r>
@@ -35,16 +59,18 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">Project Name: </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
       </rPr>
       <t>BAMF</t>
     </r>
@@ -52,16 +78,18 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
       </rPr>
       <t xml:space="preserve">Team Member Name: </t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
       </rPr>
       <t>Jacob Silber</t>
     </r>
@@ -167,9 +195,6 @@
   </si>
   <si>
     <t>85-265VAC</t>
-  </si>
-  <si>
-    <t>24V</t>
   </si>
   <si>
     <t>Power rails connected to External Power Source 1</t>
@@ -184,22 +209,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20.0"/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -207,9 +236,21 @@
     <font>
       <b/>
       <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -217,7 +258,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -233,27 +274,39 @@
     </fill>
   </fills>
   <borders count="16">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -263,6 +316,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -277,6 +331,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -288,6 +343,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -296,6 +353,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -304,158 +364,174 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-    </border>
-    <border>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="32">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -645,467 +721,488 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="C4:L35"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="8" max="8" width="19.13"/>
+    <col min="8" max="8" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="3:12" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="C4" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="C5" s="4" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="C6" s="4" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7">
-      <c r="C7" s="4" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+    </row>
+    <row r="7" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="9" ht="54.75" customHeight="1">
-      <c r="C9" s="5" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="9" spans="3:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="7"/>
-      <c r="D10" s="8" t="s">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C10" s="17"/>
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4">
         <v>2.37</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="4">
         <v>2.37</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="10"/>
-      <c r="D11" s="8" t="s">
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C11" s="18"/>
+      <c r="D11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>92.0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>92.0</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4">
+        <v>92</v>
+      </c>
+      <c r="I11" s="4">
+        <v>92</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="11"/>
-      <c r="D12" s="8" t="s">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="3:12" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C12" s="19"/>
+      <c r="D12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>500.0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>500.0</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <v>500</v>
+      </c>
+      <c r="I12" s="4">
+        <v>500</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="16" ht="56.25" customHeight="1">
-      <c r="C16" s="13" t="s">
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="16" spans="3:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17">
-      <c r="C17" s="14"/>
-      <c r="D17" s="8" t="s">
+    <row r="17" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C17" s="20"/>
+      <c r="D17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="9">
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
         <v>2.37</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="4">
         <v>2.37</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18">
-      <c r="C18" s="15"/>
-      <c r="D18" s="8" t="s">
+    <row r="18" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C18" s="21"/>
+      <c r="D18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>92.0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>92.0</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="G18" s="4">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4">
+        <v>92</v>
+      </c>
+      <c r="I18" s="4">
+        <v>92</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19">
-      <c r="C19" s="15"/>
-      <c r="D19" s="8" t="s">
+    <row r="19" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C19" s="21"/>
+      <c r="D19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H19" s="9">
-        <v>500.0</v>
-      </c>
-      <c r="I19" s="9">
-        <v>500.0</v>
-      </c>
-      <c r="J19" s="9" t="s">
+      <c r="G19" s="4">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4">
+        <v>500</v>
+      </c>
+      <c r="I19" s="4">
+        <v>500</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" s="15"/>
-      <c r="H20" s="16" t="s">
+    <row r="20" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="8">
         <f>SUM(I17:I19)</f>
         <v>594.37</v>
       </c>
-      <c r="J20" s="18" t="s">
+      <c r="J20" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21">
-      <c r="C21" s="15"/>
-      <c r="H21" s="16" t="s">
+    <row r="21" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C21" s="21"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="9">
         <v>0.25</v>
       </c>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="15"/>
-      <c r="H22" s="20" t="s">
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C22" s="21"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="8">
         <f>I20*(1+I21)</f>
-        <v>742.9625</v>
-      </c>
-      <c r="J22" s="18" t="s">
+        <v>742.96249999999998</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23">
-      <c r="C23" s="15"/>
-      <c r="H23" s="21"/>
-      <c r="J23" s="22"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="12" t="s">
+    <row r="23" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C23" s="21"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="24"/>
+    </row>
+    <row r="24" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="18">
-        <v>1.0</v>
-      </c>
-      <c r="H24" s="18">
-        <v>1500.0</v>
-      </c>
-      <c r="I24" s="18">
-        <v>1500.0</v>
-      </c>
-      <c r="J24" s="18" t="s">
+      <c r="G24" s="8">
+        <v>1</v>
+      </c>
+      <c r="H24" s="8">
+        <v>1500</v>
+      </c>
+      <c r="I24" s="8">
+        <v>1500</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24" t="s">
+    <row r="25" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="17">
+      <c r="G25" s="14"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="8">
         <f>I24-I22</f>
-        <v>757.0375</v>
-      </c>
-      <c r="J25" s="18" t="s">
+        <v>757.03750000000002</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29">
-      <c r="C29" s="25" t="s">
+    <row r="29" spans="3:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="C29" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="26" t="s">
+      <c r="G29" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="H29" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I29" s="26" t="s">
+      <c r="I29" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="J29" s="26" t="s">
+      <c r="J29" s="12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30">
-      <c r="C30" s="8" t="s">
+    <row r="30" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="C30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="8">
+        <v>12</v>
+      </c>
+      <c r="H30" s="8">
+        <v>2500</v>
+      </c>
+      <c r="I30" s="8">
+        <v>2500</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C31" s="5"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="27"/>
+    </row>
+    <row r="32" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C32" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="18">
-        <v>2500.0</v>
-      </c>
-      <c r="I30" s="18">
-        <v>2500.0</v>
-      </c>
-      <c r="J30" s="18" t="s">
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
+    </row>
+    <row r="33" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C33" s="18"/>
+      <c r="D33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1500</v>
+      </c>
+      <c r="I33" s="8">
+        <v>1500</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31">
-      <c r="C31" s="23"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="29"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="33"/>
-    </row>
-    <row r="33">
-      <c r="C33" s="10"/>
-      <c r="D33" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G33" s="18" t="s">
+    <row r="34" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C34" s="18"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C35" s="19"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H33" s="18">
-        <v>1500.0</v>
-      </c>
-      <c r="I33" s="18">
-        <v>1500.0</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" s="10"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="3"/>
-    </row>
-    <row r="35">
-      <c r="C35" s="11"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="17">
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="8">
         <f>I30-I33</f>
         <v>1000</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="J35" s="8" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C4:J4"/>
     <mergeCell ref="E35:H35"/>
     <mergeCell ref="D34:J34"/>
     <mergeCell ref="C10:C12"/>
@@ -1118,8 +1215,7 @@
     <mergeCell ref="D20:G23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D31:J32"/>
-    <mergeCell ref="C4:J4"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/05-Power-Budget/PowerBudget.xlsx
+++ b/05-Power-Budget/PowerBudget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e6f92803327c9ad0/Documents/EGR 304/jsilber27_EGR304_F26.github.io-1/docs/05-Power-Budget/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_0454703C4A55ECA9EDEB81173C2076994B823C75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{876A6AB5-8ECC-43B4-BAE3-D2371E6192F0}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_0454703C4A55ECA9EDEB81173C2076994B823C75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E86EA7-A6A5-40C0-BD7A-CB47C624637F}"/>
   <bookViews>
-    <workbookView xWindow="5124" yWindow="1956" windowWidth="16356" windowHeight="13296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5124" yWindow="384" windowWidth="16356" windowHeight="13296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -191,9 +191,6 @@
     <t>Plug-in Wall Supply</t>
   </si>
   <si>
-    <t>YS39-2402500-D1J</t>
-  </si>
-  <si>
     <t>85-265VAC</t>
   </si>
   <si>
@@ -204,6 +201,9 @@
   </si>
   <si>
     <t>Total Remaining Current Available on External Power Source 1</t>
+  </si>
+  <si>
+    <t>NGE30U12-P1J</t>
   </si>
 </sst>
 </file>
@@ -488,11 +488,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -510,9 +513,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -528,6 +528,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -738,7 +742,7 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:12" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="14"/>
@@ -750,21 +754,21 @@
       <c r="J4" s="15"/>
     </row>
     <row r="5" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="15"/>
     </row>
     <row r="6" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="15"/>
     </row>
     <row r="7" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="14"/>
@@ -799,7 +803,7 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C10" s="17"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
@@ -825,7 +829,7 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="3:12" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C11" s="18"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="3" t="s">
         <v>16</v>
       </c>
@@ -851,7 +855,7 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="3:12" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="C12" s="19"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="3" t="s">
         <v>19</v>
       </c>
@@ -903,7 +907,7 @@
       </c>
     </row>
     <row r="17" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C17" s="20"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="3" t="s">
         <v>12</v>
       </c>
@@ -927,7 +931,7 @@
       </c>
     </row>
     <row r="18" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C18" s="21"/>
+      <c r="C18" s="22"/>
       <c r="D18" s="3" t="s">
         <v>16</v>
       </c>
@@ -951,7 +955,7 @@
       </c>
     </row>
     <row r="19" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="C19" s="21"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="3" t="s">
         <v>19</v>
       </c>
@@ -975,11 +979,11 @@
       </c>
     </row>
     <row r="20" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C20" s="21"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
       <c r="H20" s="7" t="s">
         <v>23</v>
       </c>
@@ -992,11 +996,11 @@
       </c>
     </row>
     <row r="21" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C21" s="21"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
       <c r="H21" s="7" t="s">
         <v>24</v>
       </c>
@@ -1006,11 +1010,11 @@
       <c r="J21" s="8"/>
     </row>
     <row r="22" spans="3:10" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="C22" s="21"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
       <c r="H22" s="10" t="s">
         <v>25</v>
       </c>
@@ -1023,14 +1027,14 @@
       </c>
     </row>
     <row r="23" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C23" s="21"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="24"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
@@ -1062,7 +1066,7 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="16" t="s">
         <v>30</v>
       </c>
       <c r="G25" s="14"/>
@@ -1109,10 +1113,10 @@
         <v>35</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="G30" s="8">
         <v>12</v>
@@ -1129,28 +1133,28 @@
     </row>
     <row r="31" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C31" s="5"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="27"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
     </row>
     <row r="32" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C32" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="30"/>
+      <c r="C32" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="29"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="31"/>
     </row>
     <row r="33" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C33" s="18"/>
+      <c r="C33" s="19"/>
       <c r="D33" s="5" t="s">
         <v>27</v>
       </c>
@@ -1161,7 +1165,7 @@
         <v>29</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H33" s="8">
         <v>1500</v>
@@ -1174,8 +1178,8 @@
       </c>
     </row>
     <row r="34" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C34" s="18"/>
-      <c r="D34" s="16"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="17"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
@@ -1184,10 +1188,10 @@
       <c r="J34" s="15"/>
     </row>
     <row r="35" spans="3:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="C35" s="19"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="13" t="s">
-        <v>40</v>
+      <c r="E35" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
@@ -1217,5 +1221,6 @@
     <mergeCell ref="D31:J32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>